--- a/output/Data and Chart Outputs/us_mexico_pipeline_capacity.xlsx
+++ b/output/Data and Chart Outputs/us_mexico_pipeline_capacity.xlsx
@@ -23,9 +23,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="yyyy"/>
-    <numFmt numFmtId="167" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="yyyy"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -65,13 +65,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1060,7 +1062,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
@@ -1147,7 +1148,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="6" t="n">
         <v>40179</v>
       </c>
       <c r="B2" t="n">
@@ -1176,7 +1177,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="6" t="n">
         <v>40544</v>
       </c>
       <c r="B3" t="n">
@@ -1205,7 +1206,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="6" t="n">
         <v>40909</v>
       </c>
       <c r="B4" t="n">
@@ -1234,7 +1235,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="6" t="n">
         <v>41275</v>
       </c>
       <c r="B5" t="n">
@@ -1263,7 +1264,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="6" t="n">
         <v>41640</v>
       </c>
       <c r="B6" t="n">
@@ -1292,7 +1293,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="6" t="n">
         <v>42005</v>
       </c>
       <c r="B7" t="n">
@@ -1321,7 +1322,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="6" t="n">
         <v>42370</v>
       </c>
       <c r="B8" t="n">
@@ -1350,7 +1351,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="6" t="n">
         <v>42736</v>
       </c>
       <c r="B9" t="n">
@@ -1379,7 +1380,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="6" t="n">
         <v>43101</v>
       </c>
       <c r="B10" t="n">
@@ -1408,7 +1409,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="6" t="n">
         <v>43466</v>
       </c>
       <c r="B11" t="n">
@@ -1437,7 +1438,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="6" t="n">
         <v>43831</v>
       </c>
       <c r="B12" t="n">
@@ -1466,7 +1467,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="6" t="n">
         <v>44197</v>
       </c>
       <c r="B13" t="n">
@@ -1495,7 +1496,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="6" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1524,7 +1525,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="6" t="n">
         <v>44927</v>
       </c>
       <c r="B15" t="n">
@@ -1553,7 +1554,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="6" t="n">
         <v>45292</v>
       </c>
       <c r="B16" t="n">
@@ -1582,7 +1583,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="6" t="n">
         <v>45658</v>
       </c>
       <c r="B17" t="n">
@@ -1646,7 +1647,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n">
+      <c r="A2" s="7" t="n">
         <v>42005</v>
       </c>
       <c r="B2" t="n">
@@ -1657,7 +1658,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="7" t="n">
         <v>42036</v>
       </c>
       <c r="B3" t="n">
@@ -1668,7 +1669,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="7" t="n">
         <v>42064</v>
       </c>
       <c r="B4" t="n">
@@ -1679,7 +1680,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="7" t="n">
         <v>42095</v>
       </c>
       <c r="B5" t="n">
@@ -1690,7 +1691,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="7" t="n">
         <v>42125</v>
       </c>
       <c r="B6" t="n">
@@ -1701,7 +1702,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="7" t="n">
         <v>42156</v>
       </c>
       <c r="B7" t="n">
@@ -1712,7 +1713,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="7" t="n">
         <v>42186</v>
       </c>
       <c r="B8" t="n">
@@ -1723,7 +1724,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="7" t="n">
         <v>42217</v>
       </c>
       <c r="B9" t="n">
@@ -1734,7 +1735,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="7" t="n">
         <v>42248</v>
       </c>
       <c r="B10" t="n">
@@ -1745,7 +1746,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="7" t="n">
         <v>42278</v>
       </c>
       <c r="B11" t="n">
@@ -1756,7 +1757,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="7" t="n">
         <v>42309</v>
       </c>
       <c r="B12" t="n">
@@ -1767,7 +1768,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="7" t="n">
         <v>42339</v>
       </c>
       <c r="B13" t="n">
@@ -1778,7 +1779,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="7" t="n">
         <v>42370</v>
       </c>
       <c r="B14" t="n">
@@ -1789,7 +1790,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" s="7" t="n">
         <v>42401</v>
       </c>
       <c r="B15" t="n">
@@ -1800,7 +1801,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="7" t="n">
         <v>42430</v>
       </c>
       <c r="B16" t="n">
@@ -1811,7 +1812,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="7" t="n">
         <v>42461</v>
       </c>
       <c r="B17" t="n">
@@ -1822,7 +1823,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="7" t="n">
         <v>42491</v>
       </c>
       <c r="B18" t="n">
@@ -1833,7 +1834,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="7" t="n">
         <v>42522</v>
       </c>
       <c r="B19" t="n">
@@ -1844,7 +1845,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
+      <c r="A20" s="7" t="n">
         <v>42552</v>
       </c>
       <c r="B20" t="n">
@@ -1855,7 +1856,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" s="7" t="n">
         <v>42583</v>
       </c>
       <c r="B21" t="n">
@@ -1866,7 +1867,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n">
+      <c r="A22" s="7" t="n">
         <v>42614</v>
       </c>
       <c r="B22" t="n">
@@ -1877,7 +1878,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
+      <c r="A23" s="7" t="n">
         <v>42644</v>
       </c>
       <c r="B23" t="n">
@@ -1888,7 +1889,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n">
+      <c r="A24" s="7" t="n">
         <v>42675</v>
       </c>
       <c r="B24" t="n">
@@ -1899,7 +1900,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n">
+      <c r="A25" s="7" t="n">
         <v>42705</v>
       </c>
       <c r="B25" t="n">
@@ -1910,7 +1911,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n">
+      <c r="A26" s="7" t="n">
         <v>42736</v>
       </c>
       <c r="B26" t="n">
@@ -1921,7 +1922,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="7" t="n">
         <v>42767</v>
       </c>
       <c r="B27" t="n">
@@ -1932,7 +1933,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="n">
+      <c r="A28" s="7" t="n">
         <v>42795</v>
       </c>
       <c r="B28" t="n">
@@ -1943,7 +1944,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n">
+      <c r="A29" s="7" t="n">
         <v>42826</v>
       </c>
       <c r="B29" t="n">
@@ -1954,7 +1955,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="n">
+      <c r="A30" s="7" t="n">
         <v>42856</v>
       </c>
       <c r="B30" t="n">
@@ -1965,7 +1966,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
+      <c r="A31" s="7" t="n">
         <v>42887</v>
       </c>
       <c r="B31" t="n">
@@ -1976,7 +1977,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="n">
+      <c r="A32" s="7" t="n">
         <v>42917</v>
       </c>
       <c r="B32" t="n">
@@ -1987,7 +1988,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n">
+      <c r="A33" s="7" t="n">
         <v>42948</v>
       </c>
       <c r="B33" t="n">
@@ -1998,7 +1999,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="n">
+      <c r="A34" s="7" t="n">
         <v>42979</v>
       </c>
       <c r="B34" t="n">
@@ -2009,7 +2010,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="n">
+      <c r="A35" s="7" t="n">
         <v>43009</v>
       </c>
       <c r="B35" t="n">
@@ -2020,7 +2021,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="n">
+      <c r="A36" s="7" t="n">
         <v>43040</v>
       </c>
       <c r="B36" t="n">
@@ -2031,7 +2032,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="n">
+      <c r="A37" s="7" t="n">
         <v>43070</v>
       </c>
       <c r="B37" t="n">
@@ -2042,7 +2043,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="n">
+      <c r="A38" s="7" t="n">
         <v>43101</v>
       </c>
       <c r="B38" t="n">
@@ -2053,7 +2054,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n">
+      <c r="A39" s="7" t="n">
         <v>43132</v>
       </c>
       <c r="B39" t="n">
@@ -2064,7 +2065,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="n">
+      <c r="A40" s="7" t="n">
         <v>43160</v>
       </c>
       <c r="B40" t="n">
@@ -2075,7 +2076,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n">
+      <c r="A41" s="7" t="n">
         <v>43191</v>
       </c>
       <c r="B41" t="n">
@@ -2086,7 +2087,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="n">
+      <c r="A42" s="7" t="n">
         <v>43221</v>
       </c>
       <c r="B42" t="n">
@@ -2097,7 +2098,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="n">
+      <c r="A43" s="7" t="n">
         <v>43252</v>
       </c>
       <c r="B43" t="n">
@@ -2108,7 +2109,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="n">
+      <c r="A44" s="7" t="n">
         <v>43282</v>
       </c>
       <c r="B44" t="n">
@@ -2119,7 +2120,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="n">
+      <c r="A45" s="7" t="n">
         <v>43313</v>
       </c>
       <c r="B45" t="n">
@@ -2130,7 +2131,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="n">
+      <c r="A46" s="7" t="n">
         <v>43344</v>
       </c>
       <c r="B46" t="n">
@@ -2141,7 +2142,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="n">
+      <c r="A47" s="7" t="n">
         <v>43374</v>
       </c>
       <c r="B47" t="n">
@@ -2152,7 +2153,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="n">
+      <c r="A48" s="7" t="n">
         <v>43405</v>
       </c>
       <c r="B48" t="n">
@@ -2163,7 +2164,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="n">
+      <c r="A49" s="7" t="n">
         <v>43435</v>
       </c>
       <c r="B49" t="n">
@@ -2174,7 +2175,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="n">
+      <c r="A50" s="7" t="n">
         <v>43466</v>
       </c>
       <c r="B50" t="n">
@@ -2185,7 +2186,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="n">
+      <c r="A51" s="7" t="n">
         <v>43497</v>
       </c>
       <c r="B51" t="n">
@@ -2196,7 +2197,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="n">
+      <c r="A52" s="7" t="n">
         <v>43525</v>
       </c>
       <c r="B52" t="n">
@@ -2207,7 +2208,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="n">
+      <c r="A53" s="7" t="n">
         <v>43556</v>
       </c>
       <c r="B53" t="n">
@@ -2218,7 +2219,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="n">
+      <c r="A54" s="7" t="n">
         <v>43586</v>
       </c>
       <c r="B54" t="n">
@@ -2229,7 +2230,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="n">
+      <c r="A55" s="7" t="n">
         <v>43617</v>
       </c>
       <c r="B55" t="n">
@@ -2240,7 +2241,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="n">
+      <c r="A56" s="7" t="n">
         <v>43647</v>
       </c>
       <c r="B56" t="n">
@@ -2251,7 +2252,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="n">
+      <c r="A57" s="7" t="n">
         <v>43678</v>
       </c>
       <c r="B57" t="n">
@@ -2262,7 +2263,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="n">
+      <c r="A58" s="7" t="n">
         <v>43709</v>
       </c>
       <c r="B58" t="n">
@@ -2273,7 +2274,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="n">
+      <c r="A59" s="7" t="n">
         <v>43739</v>
       </c>
       <c r="B59" t="n">
@@ -2284,7 +2285,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="n">
+      <c r="A60" s="7" t="n">
         <v>43770</v>
       </c>
       <c r="B60" t="n">
@@ -2295,7 +2296,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="n">
+      <c r="A61" s="7" t="n">
         <v>43800</v>
       </c>
       <c r="B61" t="n">
@@ -2306,7 +2307,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="n">
+      <c r="A62" s="7" t="n">
         <v>43831</v>
       </c>
       <c r="B62" t="n">
@@ -2317,7 +2318,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="n">
+      <c r="A63" s="7" t="n">
         <v>43862</v>
       </c>
       <c r="B63" t="n">
@@ -2328,7 +2329,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="n">
+      <c r="A64" s="7" t="n">
         <v>43891</v>
       </c>
       <c r="B64" t="n">
@@ -2339,7 +2340,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="n">
+      <c r="A65" s="7" t="n">
         <v>43922</v>
       </c>
       <c r="B65" t="n">
@@ -2350,7 +2351,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="n">
+      <c r="A66" s="7" t="n">
         <v>43952</v>
       </c>
       <c r="B66" t="n">
@@ -2361,7 +2362,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="n">
+      <c r="A67" s="7" t="n">
         <v>43983</v>
       </c>
       <c r="B67" t="n">
@@ -2372,7 +2373,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="n">
+      <c r="A68" s="7" t="n">
         <v>44013</v>
       </c>
       <c r="B68" t="n">
@@ -2383,7 +2384,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="n">
+      <c r="A69" s="7" t="n">
         <v>44044</v>
       </c>
       <c r="B69" t="n">
@@ -2394,7 +2395,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="n">
+      <c r="A70" s="7" t="n">
         <v>44075</v>
       </c>
       <c r="B70" t="n">
@@ -2405,7 +2406,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="n">
+      <c r="A71" s="7" t="n">
         <v>44105</v>
       </c>
       <c r="B71" t="n">
@@ -2416,7 +2417,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="n">
+      <c r="A72" s="7" t="n">
         <v>44136</v>
       </c>
       <c r="B72" t="n">
@@ -2427,7 +2428,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="n">
+      <c r="A73" s="7" t="n">
         <v>44166</v>
       </c>
       <c r="B73" t="n">
@@ -2438,7 +2439,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="n">
+      <c r="A74" s="7" t="n">
         <v>44197</v>
       </c>
       <c r="B74" t="n">
@@ -2449,7 +2450,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="n">
+      <c r="A75" s="7" t="n">
         <v>44228</v>
       </c>
       <c r="B75" t="n">
@@ -2460,7 +2461,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="n">
+      <c r="A76" s="7" t="n">
         <v>44256</v>
       </c>
       <c r="B76" t="n">
@@ -2471,7 +2472,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="n">
+      <c r="A77" s="7" t="n">
         <v>44287</v>
       </c>
       <c r="B77" t="n">
@@ -2482,7 +2483,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="n">
+      <c r="A78" s="7" t="n">
         <v>44317</v>
       </c>
       <c r="B78" t="n">
@@ -2493,7 +2494,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="n">
+      <c r="A79" s="7" t="n">
         <v>44348</v>
       </c>
       <c r="B79" t="n">
@@ -2504,7 +2505,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="n">
+      <c r="A80" s="7" t="n">
         <v>44378</v>
       </c>
       <c r="B80" t="n">
@@ -2515,7 +2516,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="n">
+      <c r="A81" s="7" t="n">
         <v>44409</v>
       </c>
       <c r="B81" t="n">
@@ -2526,7 +2527,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="n">
+      <c r="A82" s="7" t="n">
         <v>44440</v>
       </c>
       <c r="B82" t="n">
@@ -2537,7 +2538,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="n">
+      <c r="A83" s="7" t="n">
         <v>44470</v>
       </c>
       <c r="B83" t="n">
@@ -2548,7 +2549,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="n">
+      <c r="A84" s="7" t="n">
         <v>44501</v>
       </c>
       <c r="B84" t="n">
@@ -2559,7 +2560,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="n">
+      <c r="A85" s="7" t="n">
         <v>44531</v>
       </c>
       <c r="B85" t="n">
@@ -2570,7 +2571,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="n">
+      <c r="A86" s="7" t="n">
         <v>44562</v>
       </c>
       <c r="B86" t="n">
@@ -2581,7 +2582,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="n">
+      <c r="A87" s="7" t="n">
         <v>44593</v>
       </c>
       <c r="B87" t="n">
@@ -2592,7 +2593,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="n">
+      <c r="A88" s="7" t="n">
         <v>44621</v>
       </c>
       <c r="B88" t="n">
@@ -2603,7 +2604,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="4" t="n">
+      <c r="A89" s="7" t="n">
         <v>44652</v>
       </c>
       <c r="B89" t="n">
@@ -2614,7 +2615,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="n">
+      <c r="A90" s="7" t="n">
         <v>44682</v>
       </c>
       <c r="B90" t="n">
@@ -2625,7 +2626,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="n">
+      <c r="A91" s="7" t="n">
         <v>44713</v>
       </c>
       <c r="B91" t="n">
@@ -2636,7 +2637,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="4" t="n">
+      <c r="A92" s="7" t="n">
         <v>44743</v>
       </c>
       <c r="B92" t="n">
@@ -2647,7 +2648,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="n">
+      <c r="A93" s="7" t="n">
         <v>44774</v>
       </c>
       <c r="B93" t="n">
@@ -2658,7 +2659,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="4" t="n">
+      <c r="A94" s="7" t="n">
         <v>44805</v>
       </c>
       <c r="B94" t="n">
@@ -2669,7 +2670,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="n">
+      <c r="A95" s="7" t="n">
         <v>44835</v>
       </c>
       <c r="B95" t="n">
@@ -2680,7 +2681,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="4" t="n">
+      <c r="A96" s="7" t="n">
         <v>44866</v>
       </c>
       <c r="B96" t="n">
@@ -2691,7 +2692,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="n">
+      <c r="A97" s="7" t="n">
         <v>44896</v>
       </c>
       <c r="B97" t="n">
@@ -2702,7 +2703,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="4" t="n">
+      <c r="A98" s="7" t="n">
         <v>44927</v>
       </c>
       <c r="B98" t="n">
@@ -2713,7 +2714,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="n">
+      <c r="A99" s="7" t="n">
         <v>44958</v>
       </c>
       <c r="B99" t="n">
@@ -2724,7 +2725,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="4" t="n">
+      <c r="A100" s="7" t="n">
         <v>44986</v>
       </c>
       <c r="B100" t="n">
@@ -2735,7 +2736,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="4" t="n">
+      <c r="A101" s="7" t="n">
         <v>45017</v>
       </c>
       <c r="B101" t="n">
@@ -2746,7 +2747,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="4" t="n">
+      <c r="A102" s="7" t="n">
         <v>45047</v>
       </c>
       <c r="B102" t="n">
@@ -2757,7 +2758,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="4" t="n">
+      <c r="A103" s="7" t="n">
         <v>45078</v>
       </c>
       <c r="B103" t="n">
@@ -2768,7 +2769,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="4" t="n">
+      <c r="A104" s="7" t="n">
         <v>45108</v>
       </c>
       <c r="B104" t="n">
@@ -2779,7 +2780,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="4" t="n">
+      <c r="A105" s="7" t="n">
         <v>45139</v>
       </c>
       <c r="B105" t="n">
@@ -2790,7 +2791,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="4" t="n">
+      <c r="A106" s="7" t="n">
         <v>45170</v>
       </c>
       <c r="B106" t="n">
@@ -2801,7 +2802,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="4" t="n">
+      <c r="A107" s="7" t="n">
         <v>45200</v>
       </c>
       <c r="B107" t="n">
@@ -2812,7 +2813,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="4" t="n">
+      <c r="A108" s="7" t="n">
         <v>45231</v>
       </c>
       <c r="B108" t="n">
@@ -2823,7 +2824,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="4" t="n">
+      <c r="A109" s="7" t="n">
         <v>45261</v>
       </c>
       <c r="B109" t="n">
@@ -2834,7 +2835,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="4" t="n">
+      <c r="A110" s="7" t="n">
         <v>45292</v>
       </c>
       <c r="B110" t="n">
@@ -2845,7 +2846,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="n">
+      <c r="A111" s="7" t="n">
         <v>45323</v>
       </c>
       <c r="B111" t="n">
@@ -2856,7 +2857,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="4" t="n">
+      <c r="A112" s="7" t="n">
         <v>45352</v>
       </c>
       <c r="B112" t="n">
@@ -2867,7 +2868,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="4" t="n">
+      <c r="A113" s="7" t="n">
         <v>45383</v>
       </c>
       <c r="B113" t="n">
@@ -2878,7 +2879,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="4" t="n">
+      <c r="A114" s="7" t="n">
         <v>45413</v>
       </c>
       <c r="B114" t="n">
@@ -2889,7 +2890,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="4" t="n">
+      <c r="A115" s="7" t="n">
         <v>45444</v>
       </c>
       <c r="B115" t="n">
@@ -2900,7 +2901,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="4" t="n">
+      <c r="A116" s="7" t="n">
         <v>45474</v>
       </c>
       <c r="B116" t="n">
@@ -2911,7 +2912,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="4" t="n">
+      <c r="A117" s="7" t="n">
         <v>45505</v>
       </c>
       <c r="B117" t="n">
@@ -2922,7 +2923,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="4" t="n">
+      <c r="A118" s="7" t="n">
         <v>45536</v>
       </c>
       <c r="B118" t="n">
@@ -2933,7 +2934,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="4" t="n">
+      <c r="A119" s="7" t="n">
         <v>45566</v>
       </c>
       <c r="B119" t="n">
@@ -2944,7 +2945,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="4" t="n">
+      <c r="A120" s="7" t="n">
         <v>45597</v>
       </c>
       <c r="B120" t="n">
@@ -2955,7 +2956,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="4" t="n">
+      <c r="A121" s="7" t="n">
         <v>45627</v>
       </c>
       <c r="B121" t="n">
@@ -2966,7 +2967,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="4" t="n">
+      <c r="A122" s="7" t="n">
         <v>45658</v>
       </c>
       <c r="B122" t="n">
@@ -2977,7 +2978,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="4" t="n">
+      <c r="A123" s="7" t="n">
         <v>45689</v>
       </c>
       <c r="B123" t="n">
@@ -2988,7 +2989,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="4" t="n">
+      <c r="A124" s="7" t="n">
         <v>45717</v>
       </c>
       <c r="B124" t="n">
@@ -2999,7 +3000,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="4" t="n">
+      <c r="A125" s="7" t="n">
         <v>45748</v>
       </c>
       <c r="B125" t="n">
@@ -3010,7 +3011,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="4" t="n">
+      <c r="A126" s="7" t="n">
         <v>45778</v>
       </c>
       <c r="B126" t="n">
@@ -3021,7 +3022,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="4" t="n">
+      <c r="A127" s="7" t="n">
         <v>45809</v>
       </c>
       <c r="B127" t="n">
@@ -3032,7 +3033,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="4" t="n">
+      <c r="A128" s="7" t="n">
         <v>45839</v>
       </c>
       <c r="B128" t="n">
@@ -3043,7 +3044,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="4" t="n">
+      <c r="A129" s="7" t="n">
         <v>45870</v>
       </c>
       <c r="B129" t="n">
@@ -3054,7 +3055,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="4" t="n">
+      <c r="A130" s="7" t="n">
         <v>45901</v>
       </c>
       <c r="B130" t="n">
@@ -3065,7 +3066,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="4" t="n">
+      <c r="A131" s="7" t="n">
         <v>45931</v>
       </c>
       <c r="B131" t="n">
@@ -3076,7 +3077,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="4" t="n">
+      <c r="A132" s="7" t="n">
         <v>45962</v>
       </c>
       <c r="B132" t="n">
@@ -3087,7 +3088,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="4" t="n">
+      <c r="A133" s="7" t="n">
         <v>45992</v>
       </c>
       <c r="B133" t="n">
@@ -3098,7 +3099,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="4" t="n">
+      <c r="A134" s="7" t="n">
         <v>46023</v>
       </c>
       <c r="B134" t="n">
@@ -3109,7 +3110,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="4" t="n">
+      <c r="A135" s="7" t="n">
         <v>46054</v>
       </c>
       <c r="B135" t="n">
@@ -3120,7 +3121,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="4" t="n">
+      <c r="A136" s="7" t="n">
         <v>46082</v>
       </c>
       <c r="B136" t="n">
@@ -3131,7 +3132,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="4" t="n">
+      <c r="A137" s="7" t="n">
         <v>46113</v>
       </c>
       <c r="B137" t="n">
@@ -3142,7 +3143,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="4" t="n">
+      <c r="A138" s="7" t="n">
         <v>46143</v>
       </c>
       <c r="B138" t="n">
@@ -3153,7 +3154,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="4" t="n">
+      <c r="A139" s="7" t="n">
         <v>46174</v>
       </c>
       <c r="B139" t="n">
@@ -3164,7 +3165,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="4" t="n">
+      <c r="A140" s="7" t="n">
         <v>46204</v>
       </c>
       <c r="B140" t="n">

--- a/output/Data and Chart Outputs/us_mexico_pipeline_capacity.xlsx
+++ b/output/Data and Chart Outputs/us_mexico_pipeline_capacity.xlsx
@@ -162,6 +162,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>US to Mexico gas pipeline capacity by line (EIA) (to 2025)</a:t>
             </a:r>
           </a:p>
@@ -493,6 +494,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>US pipeline exports to Mexico vs pipeline capacity (EIA) (to Jul/26)</a:t>
             </a:r>
           </a:p>
